--- a/2022/Bekaa2/Bekaa2_members_final.xlsx
+++ b/2022/Bekaa2/Bekaa2_members_final.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
